--- a/output/pdf_financials_xlsx/SCV.xlsx
+++ b/output/pdf_financials_xlsx/SCV.xlsx
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.633901</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.022641</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.117341</v>
       </c>
     </row>
     <row r="93">
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.937098</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>9.066647</v>
+        <v>8.918336</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0.032411</v>
@@ -3104,7 +3104,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3609,7 +3613,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.633901</v>
       </c>
@@ -4349,7 +4357,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>-0.937098</v>
       </c>

--- a/output/pdf_financials_xlsx/SCV.xlsx
+++ b/output/pdf_financials_xlsx/SCV.xlsx
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.218714</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.014222</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009726</v>
       </c>
     </row>
     <row r="35">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.218714</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.014222</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009726</v>
       </c>
     </row>
     <row r="37">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.234437</v>
+        <v>0.015723</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.03017</v>
+        <v>0.015948</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.031825</v>
+        <v>0.022099</v>
       </c>
     </row>
     <row r="49">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/SCV.xlsx
+++ b/output/pdf_financials_xlsx/SCV.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.24</v>
+        <v>0.276</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.24</v>
+        <v>0.276</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.265</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="8">
@@ -4613,7 +4613,11 @@
           <t>Directors' fees 10</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.036</v>
       </c>
